--- a/docs/StructureDefinition-MedDispenseRefillMedicationDispense.xlsx
+++ b/docs/StructureDefinition-MedDispenseRefillMedicationDispense.xlsx
@@ -57,13 +57,13 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-10-17T15:32:01+00:00</t>
+    <t>2023-10-31T15:37:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
   </si>
   <si>
-    <t>JPSys</t>
+    <t>VA</t>
   </si>
   <si>
     <t>Contact</t>

--- a/docs/StructureDefinition-MedDispenseRefillMedicationDispense.xlsx
+++ b/docs/StructureDefinition-MedDispenseRefillMedicationDispense.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-10-31T15:37:13+00:00</t>
+    <t>2023-11-01T18:52:48+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -81,7 +81,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>This StructureDefinition contains the maps for Use Case MedDispenseRefill, ResourceType MedicationDispense</t>
+    <t>This StructureDefinition contains the maps for VistA PRESCRIPTION (file 52) to FHIR MedicationDispense</t>
   </si>
   <si>
     <t>Purpose</t>

--- a/docs/StructureDefinition-MedDispenseRefillMedicationDispense.xlsx
+++ b/docs/StructureDefinition-MedDispenseRefillMedicationDispense.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-11-01T18:52:48+00:00</t>
+    <t>2023-11-08T21:21:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-MedDispenseRefillMedicationDispense.xlsx
+++ b/docs/StructureDefinition-MedDispenseRefillMedicationDispense.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-11-08T21:21:15+00:00</t>
+    <t>2023-11-08T21:56:35+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-MedDispenseRefillMedicationDispense.xlsx
+++ b/docs/StructureDefinition-MedDispenseRefillMedicationDispense.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-11-09T22:38:39+00:00</t>
+    <t>2023-11-14T14:54:31+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-MedDispenseRefillMedicationDispense.xlsx
+++ b/docs/StructureDefinition-MedDispenseRefillMedicationDispense.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-11-14T14:54:31+00:00</t>
+    <t>2023-11-14T17:25:19+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-MedDispenseRefillMedicationDispense.xlsx
+++ b/docs/StructureDefinition-MedDispenseRefillMedicationDispense.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4031" uniqueCount="701">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4031" uniqueCount="702">
   <si>
     <t>Property</t>
   </si>
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.3.0</t>
+    <t>0.4.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-11-14T17:25:19+00:00</t>
+    <t>2023-11-15T12:04:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -249,10 +249,10 @@
     <t>Mapping: HL7 v2 Mapping</t>
   </si>
   <si>
+    <t>Mapping: Veterans Health Information Systems Technology and Architecture (VistA)</t>
+  </si>
+  <si>
     <t>Mapping: Clinical Data Warehouse (CDW)</t>
-  </si>
-  <si>
-    <t>Mapping: Veterans Health Information Systems Technology and Architecture (VistA)</t>
   </si>
   <si>
     <t>Mapping: Virtual Patient Record (VPR)</t>
@@ -542,6 +542,10 @@
     <t>http://hl7.org/fhir/ValueSet/medicationdispense-status|4.0.1</t>
   </si>
   <si>
+    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+inv-34:869: fixed value "completed" {null}inv-35:819: fixed value "in-progress" {null}inv-36:1555: fixed value "in-progress" {null}</t>
+  </si>
+  <si>
     <t>Event.status</t>
   </si>
   <si>
@@ -817,6 +821,9 @@
   </si>
   <si>
     <t>C*E.1</t>
+  </si>
+  <si>
+    <t>1561: source value from PRESCRIPTION - DRUG &gt; DRUG - PSNDF VA PRODUCT NAME ENTRY (#52-6 &gt; 50-22)</t>
   </si>
   <si>
     <t>Dim.LocalDrug.DrugNameWithoutDoseIEN
@@ -824,9 +831,6 @@
 Dim.LocalDrug.NationalDrugIEN</t>
   </si>
   <si>
-    <t>1561: source value from PRESCRIPTION - DRUG &gt; DRUG - PSNDF VA PRODUCT NAME ENTRY (#52-6 &gt; 50-22)</t>
-  </si>
-  <si>
     <t>MedicationDispense.medication[x]:medicationCodeableConcept.coding.display</t>
   </si>
   <si>
@@ -907,6 +911,9 @@
   </si>
   <si>
     <t>C*E.9. But note many systems use C*E.2 for this</t>
+  </si>
+  <si>
+    <t>1560: source value from PRESCRIPTION - DRUG &gt; DRUG - GENERIC NAME (#52-6 &gt; 50-.01)</t>
   </si>
   <si>
     <t>Dim.IVAdditiveIngredient.LocalDrugNameWithDose
@@ -918,9 +925,6 @@
 RxOut.RxOutpatFill.LocalDrugNameWithDose</t>
   </si>
   <si>
-    <t>1560: source value from PRESCRIPTION - DRUG &gt; DRUG - GENERIC NAME (#52-6 &gt; 50-.01)</t>
-  </si>
-  <si>
     <t>MedicationDispense.subject</t>
   </si>
   <si>
@@ -1088,10 +1092,10 @@
     <t>.participation[typeCode=LOC].role</t>
   </si>
   <si>
+    <t>1552: reference from PRESCRIPTION - CLINIC (#52-5)</t>
+  </si>
+  <si>
     <t>RxOut.RxOutpatFill.PrescribingDivisionIEN</t>
-  </si>
-  <si>
-    <t>1552: reference from PRESCRIPTION - CLINIC (#52-5)</t>
   </si>
   <si>
     <t>Pharmacy: facility</t>
@@ -1125,10 +1129,10 @@
     <t>ORC-2 Placer Order Number</t>
   </si>
   <si>
+    <t>1553: source value from PRESCRIPTION - PLACER ORDER # (#52-39.3)</t>
+  </si>
+  <si>
     <t>RxOut.RxOutpat.CPRSOrderEntryNumber</t>
-  </si>
-  <si>
-    <t>1553: source value from PRESCRIPTION - PLACER ORDER # (#52-39.3)</t>
   </si>
   <si>
     <t>MedicationDispense.type</t>
@@ -1643,10 +1647,10 @@
     <t>Dosage.patientInstruction</t>
   </si>
   <si>
+    <t>1557: source value from PRESCRIPTION - PATIENT INSTRUCTIONS (#52-114)</t>
+  </si>
+  <si>
     <t>RxOut.RxOutpatSig.PatientInstructions</t>
-  </si>
-  <si>
-    <t>1557: source value from PRESCRIPTION - PATIENT INSTRUCTIONS (#52-114)</t>
   </si>
   <si>
     <t>MedicationDispense.dosageInstruction.timing</t>
@@ -1913,12 +1917,12 @@
     <t>MedicationDispense.dosageInstruction.doseAndRate.dose[x].value</t>
   </si>
   <si>
+    <t>1558: source value from PRESCRIPTION - MEDICATION INSTRUCTIONS &gt; MEDICATION INSTRUCTIONS - DOSAGE ORDERED (#52-113 &gt; 52.0113-.01) case number</t>
+  </si>
+  <si>
     <t>RxOut.RxOutpatMedInstructions.DoseOrdered</t>
   </si>
   <si>
-    <t>1558: source value from PRESCRIPTION - MEDICATION INSTRUCTIONS &gt; MEDICATION INSTRUCTIONS - DOSAGE ORDERED (#52-113 &gt; 52.0113-.01) case number</t>
-  </si>
-  <si>
     <t>Pharmacy: dose.dose</t>
   </si>
   <si>
@@ -1934,10 +1938,10 @@
     <t>MedicationDispense.dosageInstruction.doseAndRate.dose[x].unit</t>
   </si>
   <si>
+    <t>1559: source value from PRESCRIPTION - MEDICATION INSTRUCTIONS &gt; MEDICATION INSTRUCTIONS - UNITS (#52-113 &gt; 52.0113-2)</t>
+  </si>
+  <si>
     <t>RxOut.RxOutpatMedInstructions.Unit</t>
-  </si>
-  <si>
-    <t>1559: source value from PRESCRIPTION - MEDICATION INSTRUCTIONS &gt; MEDICATION INSTRUCTIONS - UNITS (#52-113 &gt; 52.0113-2)</t>
   </si>
   <si>
     <t>Pharmacy: dose.units</t>
@@ -2533,8 +2537,8 @@
     <col min="39" max="39" width="36.91796875" customWidth="true" bestFit="true"/>
     <col min="40" max="40" width="73.296875" customWidth="true" bestFit="true"/>
     <col min="41" max="41" width="255.0" customWidth="true" bestFit="true"/>
-    <col min="42" max="42" width="61.98046875" customWidth="true" bestFit="true"/>
-    <col min="43" max="43" width="149.8671875" customWidth="true" bestFit="true"/>
+    <col min="42" max="42" width="149.8671875" customWidth="true" bestFit="true"/>
+    <col min="43" max="43" width="61.98046875" customWidth="true" bestFit="true"/>
     <col min="44" max="44" width="40.984375" customWidth="true" bestFit="true"/>
   </cols>
   <sheetData>
@@ -4153,28 +4157,28 @@
         <v>81</v>
       </c>
       <c r="AJ13" t="s" s="2">
-        <v>103</v>
+        <v>170</v>
       </c>
       <c r="AK13" t="s" s="2">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="AL13" t="s" s="2">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="AM13" t="s" s="2">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="AN13" t="s" s="2">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="AO13" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AP13" t="s" s="2">
-        <v>81</v>
+        <v>175</v>
       </c>
       <c r="AQ13" t="s" s="2">
-        <v>174</v>
+        <v>81</v>
       </c>
       <c r="AR13" t="s" s="2">
         <v>81</v>
@@ -4182,10 +4186,10 @@
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
@@ -4208,13 +4212,13 @@
         <v>81</v>
       </c>
       <c r="K14" t="s" s="2">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="L14" t="s" s="2">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="M14" t="s" s="2">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="N14" s="2"/>
       <c r="O14" s="2"/>
@@ -4241,13 +4245,13 @@
         <v>81</v>
       </c>
       <c r="X14" t="s" s="2">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="Y14" t="s" s="2">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="Z14" t="s" s="2">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="AA14" t="s" s="2">
         <v>81</v>
@@ -4265,7 +4269,7 @@
         <v>81</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="AG14" t="s" s="2">
         <v>82</v>
@@ -4280,10 +4284,10 @@
         <v>103</v>
       </c>
       <c r="AK14" t="s" s="2">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="AL14" t="s" s="2">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="AM14" t="s" s="2">
         <v>81</v>
@@ -4306,10 +4310,10 @@
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
@@ -4332,16 +4336,16 @@
         <v>81</v>
       </c>
       <c r="K15" t="s" s="2">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="L15" t="s" s="2">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="M15" t="s" s="2">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="N15" t="s" s="2">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="O15" s="2"/>
       <c r="P15" t="s" s="2">
@@ -4370,10 +4374,10 @@
         <v>115</v>
       </c>
       <c r="Y15" t="s" s="2">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="Z15" t="s" s="2">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="AA15" t="s" s="2">
         <v>81</v>
@@ -4391,7 +4395,7 @@
         <v>81</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="AG15" t="s" s="2">
         <v>82</v>
@@ -4409,7 +4413,7 @@
         <v>81</v>
       </c>
       <c r="AL15" t="s" s="2">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="AM15" t="s" s="2">
         <v>81</v>
@@ -4432,10 +4436,10 @@
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
@@ -4458,16 +4462,16 @@
         <v>92</v>
       </c>
       <c r="K16" t="s" s="2">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="L16" t="s" s="2">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="M16" t="s" s="2">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="N16" t="s" s="2">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="O16" s="2"/>
       <c r="P16" t="s" s="2">
@@ -4493,29 +4497,29 @@
         <v>81</v>
       </c>
       <c r="X16" t="s" s="2">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="Y16" t="s" s="2">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="Z16" t="s" s="2">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="AA16" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AB16" t="s" s="2">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="AC16" s="2"/>
       <c r="AD16" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AE16" t="s" s="2">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="AG16" t="s" s="2">
         <v>91</v>
@@ -4530,19 +4534,19 @@
         <v>103</v>
       </c>
       <c r="AK16" t="s" s="2">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="AL16" t="s" s="2">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="AM16" t="s" s="2">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="AN16" t="s" s="2">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="AO16" t="s" s="2">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="AP16" t="s" s="2">
         <v>81</v>
@@ -4556,13 +4560,13 @@
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="C17" t="s" s="2">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="D17" t="s" s="2">
         <v>81</v>
@@ -4584,16 +4588,16 @@
         <v>92</v>
       </c>
       <c r="K17" t="s" s="2">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="L17" t="s" s="2">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="N17" t="s" s="2">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="O17" s="2"/>
       <c r="P17" t="s" s="2">
@@ -4619,13 +4623,13 @@
         <v>81</v>
       </c>
       <c r="X17" t="s" s="2">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="Y17" t="s" s="2">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="Z17" t="s" s="2">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="AA17" t="s" s="2">
         <v>81</v>
@@ -4643,7 +4647,7 @@
         <v>81</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>91</v>
@@ -4658,19 +4662,19 @@
         <v>103</v>
       </c>
       <c r="AK17" t="s" s="2">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="AL17" t="s" s="2">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="AM17" t="s" s="2">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="AN17" t="s" s="2">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="AO17" t="s" s="2">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="AP17" t="s" s="2">
         <v>81</v>
@@ -4684,10 +4688,10 @@
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -4710,13 +4714,13 @@
         <v>81</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="N18" s="2"/>
       <c r="O18" s="2"/>
@@ -4767,7 +4771,7 @@
         <v>81</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>82</v>
@@ -4785,7 +4789,7 @@
         <v>81</v>
       </c>
       <c r="AL18" t="s" s="2">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="AM18" t="s" s="2">
         <v>81</v>
@@ -4808,10 +4812,10 @@
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
@@ -4840,7 +4844,7 @@
         <v>138</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="N19" t="s" s="2">
         <v>140</v>
@@ -4881,19 +4885,19 @@
         <v>81</v>
       </c>
       <c r="AB19" t="s" s="2">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="AC19" t="s" s="2">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="AD19" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AE19" t="s" s="2">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>82</v>
@@ -4911,7 +4915,7 @@
         <v>81</v>
       </c>
       <c r="AL19" t="s" s="2">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="AM19" t="s" s="2">
         <v>81</v>
@@ -4934,10 +4938,10 @@
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
@@ -4960,19 +4964,19 @@
         <v>92</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="N20" t="s" s="2">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="O20" t="s" s="2">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="P20" t="s" s="2">
         <v>81</v>
@@ -5021,7 +5025,7 @@
         <v>81</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>82</v>
@@ -5039,7 +5043,7 @@
         <v>81</v>
       </c>
       <c r="AL20" t="s" s="2">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="AM20" t="s" s="2">
         <v>81</v>
@@ -5048,7 +5052,7 @@
         <v>81</v>
       </c>
       <c r="AO20" t="s" s="2">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="AP20" t="s" s="2">
         <v>81</v>
@@ -5062,10 +5066,10 @@
     </row>
     <row r="21">
       <c r="A21" t="s" s="2">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -5088,13 +5092,13 @@
         <v>81</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="N21" s="2"/>
       <c r="O21" s="2"/>
@@ -5145,7 +5149,7 @@
         <v>81</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>82</v>
@@ -5163,7 +5167,7 @@
         <v>81</v>
       </c>
       <c r="AL21" t="s" s="2">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="AM21" t="s" s="2">
         <v>81</v>
@@ -5186,10 +5190,10 @@
     </row>
     <row r="22">
       <c r="A22" t="s" s="2">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -5218,7 +5222,7 @@
         <v>138</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="N22" t="s" s="2">
         <v>140</v>
@@ -5259,19 +5263,19 @@
         <v>81</v>
       </c>
       <c r="AB22" t="s" s="2">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="AC22" t="s" s="2">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="AD22" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AE22" t="s" s="2">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>82</v>
@@ -5289,7 +5293,7 @@
         <v>81</v>
       </c>
       <c r="AL22" t="s" s="2">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="AM22" t="s" s="2">
         <v>81</v>
@@ -5312,10 +5316,10 @@
     </row>
     <row r="23">
       <c r="A23" t="s" s="2">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -5341,16 +5345,16 @@
         <v>105</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="N23" t="s" s="2">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="O23" t="s" s="2">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="P23" t="s" s="2">
         <v>81</v>
@@ -5399,7 +5403,7 @@
         <v>81</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>82</v>
@@ -5417,7 +5421,7 @@
         <v>81</v>
       </c>
       <c r="AL23" t="s" s="2">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="AM23" t="s" s="2">
         <v>81</v>
@@ -5426,7 +5430,7 @@
         <v>81</v>
       </c>
       <c r="AO23" t="s" s="2">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="AP23" t="s" s="2">
         <v>81</v>
@@ -5440,10 +5444,10 @@
     </row>
     <row r="24">
       <c r="A24" t="s" s="2">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -5466,16 +5470,16 @@
         <v>92</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="N24" t="s" s="2">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="O24" s="2"/>
       <c r="P24" t="s" s="2">
@@ -5525,7 +5529,7 @@
         <v>81</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>82</v>
@@ -5543,7 +5547,7 @@
         <v>81</v>
       </c>
       <c r="AL24" t="s" s="2">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="AM24" t="s" s="2">
         <v>81</v>
@@ -5552,7 +5556,7 @@
         <v>81</v>
       </c>
       <c r="AO24" t="s" s="2">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="AP24" t="s" s="2">
         <v>81</v>
@@ -5566,10 +5570,10 @@
     </row>
     <row r="25">
       <c r="A25" t="s" s="2">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -5595,14 +5599,14 @@
         <v>111</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="N25" s="2"/>
       <c r="O25" t="s" s="2">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="P25" t="s" s="2">
         <v>81</v>
@@ -5651,7 +5655,7 @@
         <v>81</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>82</v>
@@ -5669,7 +5673,7 @@
         <v>81</v>
       </c>
       <c r="AL25" t="s" s="2">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="AM25" t="s" s="2">
         <v>81</v>
@@ -5678,13 +5682,13 @@
         <v>81</v>
       </c>
       <c r="AO25" t="s" s="2">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="AP25" t="s" s="2">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="AQ25" t="s" s="2">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="AR25" t="s" s="2">
         <v>81</v>
@@ -5692,10 +5696,10 @@
     </row>
     <row r="26">
       <c r="A26" t="s" s="2">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -5718,17 +5722,17 @@
         <v>92</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="N26" s="2"/>
       <c r="O26" t="s" s="2">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="P26" t="s" s="2">
         <v>81</v>
@@ -5777,7 +5781,7 @@
         <v>81</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>82</v>
@@ -5795,7 +5799,7 @@
         <v>81</v>
       </c>
       <c r="AL26" t="s" s="2">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="AM26" t="s" s="2">
         <v>81</v>
@@ -5804,7 +5808,7 @@
         <v>81</v>
       </c>
       <c r="AO26" t="s" s="2">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="AP26" t="s" s="2">
         <v>81</v>
@@ -5818,10 +5822,10 @@
     </row>
     <row r="27">
       <c r="A27" t="s" s="2">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -5844,19 +5848,19 @@
         <v>92</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="N27" t="s" s="2">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="O27" t="s" s="2">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="P27" t="s" s="2">
         <v>81</v>
@@ -5905,7 +5909,7 @@
         <v>81</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>82</v>
@@ -5923,7 +5927,7 @@
         <v>81</v>
       </c>
       <c r="AL27" t="s" s="2">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="AM27" t="s" s="2">
         <v>81</v>
@@ -5932,7 +5936,7 @@
         <v>81</v>
       </c>
       <c r="AO27" t="s" s="2">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="AP27" t="s" s="2">
         <v>81</v>
@@ -5946,10 +5950,10 @@
     </row>
     <row r="28">
       <c r="A28" t="s" s="2">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -5972,19 +5976,19 @@
         <v>92</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="N28" t="s" s="2">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="O28" t="s" s="2">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="P28" t="s" s="2">
         <v>81</v>
@@ -6033,7 +6037,7 @@
         <v>81</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>82</v>
@@ -6051,7 +6055,7 @@
         <v>81</v>
       </c>
       <c r="AL28" t="s" s="2">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="AM28" t="s" s="2">
         <v>81</v>
@@ -6060,13 +6064,13 @@
         <v>81</v>
       </c>
       <c r="AO28" t="s" s="2">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="AP28" t="s" s="2">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="AQ28" t="s" s="2">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="AR28" t="s" s="2">
         <v>81</v>
@@ -6074,10 +6078,10 @@
     </row>
     <row r="29">
       <c r="A29" t="s" s="2">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -6100,16 +6104,16 @@
         <v>92</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="N29" t="s" s="2">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="O29" s="2"/>
       <c r="P29" t="s" s="2">
@@ -6159,7 +6163,7 @@
         <v>81</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>82</v>
@@ -6174,25 +6178,25 @@
         <v>103</v>
       </c>
       <c r="AK29" t="s" s="2">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="AL29" t="s" s="2">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="AM29" t="s" s="2">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="AN29" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AO29" t="s" s="2">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="AP29" t="s" s="2">
-        <v>81</v>
+        <v>301</v>
       </c>
       <c r="AQ29" t="s" s="2">
-        <v>300</v>
+        <v>81</v>
       </c>
       <c r="AR29" t="s" s="2">
         <v>81</v>
@@ -6200,10 +6204,10 @@
     </row>
     <row r="30">
       <c r="A30" t="s" s="2">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -6226,13 +6230,13 @@
         <v>81</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="N30" s="2"/>
       <c r="O30" s="2"/>
@@ -6283,7 +6287,7 @@
         <v>81</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>82</v>
@@ -6298,10 +6302,10 @@
         <v>103</v>
       </c>
       <c r="AK30" t="s" s="2">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="AL30" t="s" s="2">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="AM30" t="s" s="2">
         <v>81</v>
@@ -6324,10 +6328,10 @@
     </row>
     <row r="31">
       <c r="A31" t="s" s="2">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -6350,13 +6354,13 @@
         <v>81</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="N31" s="2"/>
       <c r="O31" s="2"/>
@@ -6407,7 +6411,7 @@
         <v>81</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>82</v>
@@ -6425,10 +6429,10 @@
         <v>81</v>
       </c>
       <c r="AL31" t="s" s="2">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="AM31" t="s" s="2">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="AN31" t="s" s="2">
         <v>81</v>
@@ -6448,10 +6452,10 @@
     </row>
     <row r="32">
       <c r="A32" t="s" s="2">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -6474,13 +6478,13 @@
         <v>81</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="N32" s="2"/>
       <c r="O32" s="2"/>
@@ -6531,7 +6535,7 @@
         <v>81</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>82</v>
@@ -6546,10 +6550,10 @@
         <v>103</v>
       </c>
       <c r="AK32" t="s" s="2">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="AL32" t="s" s="2">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="AM32" t="s" s="2">
         <v>81</v>
@@ -6572,10 +6576,10 @@
     </row>
     <row r="33">
       <c r="A33" t="s" s="2">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -6598,13 +6602,13 @@
         <v>81</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="N33" s="2"/>
       <c r="O33" s="2"/>
@@ -6655,7 +6659,7 @@
         <v>81</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>82</v>
@@ -6673,7 +6677,7 @@
         <v>81</v>
       </c>
       <c r="AL33" t="s" s="2">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="AM33" t="s" s="2">
         <v>81</v>
@@ -6696,10 +6700,10 @@
     </row>
     <row r="34">
       <c r="A34" t="s" s="2">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -6728,7 +6732,7 @@
         <v>138</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="N34" t="s" s="2">
         <v>140</v>
@@ -6781,7 +6785,7 @@
         <v>81</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>82</v>
@@ -6799,7 +6803,7 @@
         <v>81</v>
       </c>
       <c r="AL34" t="s" s="2">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="AM34" t="s" s="2">
         <v>81</v>
@@ -6822,14 +6826,14 @@
     </row>
     <row r="35">
       <c r="A35" t="s" s="2">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="E35" s="2"/>
       <c r="F35" t="s" s="2">
@@ -6851,10 +6855,10 @@
         <v>137</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="N35" t="s" s="2">
         <v>140</v>
@@ -6909,7 +6913,7 @@
         <v>81</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>82</v>
@@ -6950,10 +6954,10 @@
     </row>
     <row r="36">
       <c r="A36" t="s" s="2">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -6976,17 +6980,17 @@
         <v>81</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="N36" s="2"/>
       <c r="O36" t="s" s="2">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="P36" t="s" s="2">
         <v>81</v>
@@ -7011,13 +7015,13 @@
         <v>81</v>
       </c>
       <c r="X36" t="s" s="2">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="Y36" t="s" s="2">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="Z36" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="AA36" t="s" s="2">
         <v>81</v>
@@ -7035,7 +7039,7 @@
         <v>81</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>82</v>
@@ -7053,7 +7057,7 @@
         <v>81</v>
       </c>
       <c r="AL36" t="s" s="2">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="AM36" t="s" s="2">
         <v>81</v>
@@ -7076,10 +7080,10 @@
     </row>
     <row r="37">
       <c r="A37" t="s" s="2">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -7102,13 +7106,13 @@
         <v>81</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="N37" s="2"/>
       <c r="O37" s="2"/>
@@ -7159,7 +7163,7 @@
         <v>81</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>91</v>
@@ -7174,10 +7178,10 @@
         <v>103</v>
       </c>
       <c r="AK37" t="s" s="2">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="AL37" t="s" s="2">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="AM37" t="s" s="2">
         <v>81</v>
@@ -7200,10 +7204,10 @@
     </row>
     <row r="38">
       <c r="A38" t="s" s="2">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -7226,13 +7230,13 @@
         <v>81</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="N38" s="2"/>
       <c r="O38" s="2"/>
@@ -7283,7 +7287,7 @@
         <v>81</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>82</v>
@@ -7301,7 +7305,7 @@
         <v>81</v>
       </c>
       <c r="AL38" t="s" s="2">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="AM38" t="s" s="2">
         <v>81</v>
@@ -7313,21 +7317,21 @@
         <v>81</v>
       </c>
       <c r="AP38" t="s" s="2">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="AQ38" t="s" s="2">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="AR38" t="s" s="2">
-        <v>346</v>
+        <v>347</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="s" s="2">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -7350,16 +7354,16 @@
         <v>81</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="N39" t="s" s="2">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="O39" s="2"/>
       <c r="P39" t="s" s="2">
@@ -7409,7 +7413,7 @@
         <v>81</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>82</v>
@@ -7424,25 +7428,25 @@
         <v>103</v>
       </c>
       <c r="AK39" t="s" s="2">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="AL39" t="s" s="2">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="AM39" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN39" t="s" s="2">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="AO39" t="s" s="2">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="AP39" t="s" s="2">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="AQ39" t="s" s="2">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="AR39" t="s" s="2">
         <v>81</v>
@@ -7450,10 +7454,10 @@
     </row>
     <row r="40">
       <c r="A40" t="s" s="2">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -7476,13 +7480,13 @@
         <v>81</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="N40" s="2"/>
       <c r="O40" s="2"/>
@@ -7509,13 +7513,13 @@
         <v>81</v>
       </c>
       <c r="X40" t="s" s="2">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="Y40" t="s" s="2">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="Z40" t="s" s="2">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="AA40" t="s" s="2">
         <v>81</v>
@@ -7533,7 +7537,7 @@
         <v>81</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>82</v>
@@ -7551,16 +7555,16 @@
         <v>81</v>
       </c>
       <c r="AL40" t="s" s="2">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="AM40" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN40" t="s" s="2">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="AO40" t="s" s="2">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="AP40" t="s" s="2">
         <v>81</v>
@@ -7574,10 +7578,10 @@
     </row>
     <row r="41">
       <c r="A41" t="s" s="2">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -7600,13 +7604,13 @@
         <v>81</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="N41" s="2"/>
       <c r="O41" s="2"/>
@@ -7657,7 +7661,7 @@
         <v>81</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>82</v>
@@ -7675,16 +7679,16 @@
         <v>81</v>
       </c>
       <c r="AL41" t="s" s="2">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="AM41" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN41" t="s" s="2">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="AO41" t="s" s="2">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="AP41" t="s" s="2">
         <v>81</v>
@@ -7698,10 +7702,10 @@
     </row>
     <row r="42">
       <c r="A42" t="s" s="2">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -7724,13 +7728,13 @@
         <v>81</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="N42" s="2"/>
       <c r="O42" s="2"/>
@@ -7781,7 +7785,7 @@
         <v>81</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>82</v>
@@ -7799,7 +7803,7 @@
         <v>81</v>
       </c>
       <c r="AL42" t="s" s="2">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="AM42" t="s" s="2">
         <v>81</v>
@@ -7822,10 +7826,10 @@
     </row>
     <row r="43">
       <c r="A43" t="s" s="2">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -7854,7 +7858,7 @@
         <v>138</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="N43" t="s" s="2">
         <v>140</v>
@@ -7895,19 +7899,19 @@
         <v>81</v>
       </c>
       <c r="AB43" t="s" s="2">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="AC43" t="s" s="2">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="AD43" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AE43" t="s" s="2">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>82</v>
@@ -7925,7 +7929,7 @@
         <v>81</v>
       </c>
       <c r="AL43" t="s" s="2">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="AM43" t="s" s="2">
         <v>81</v>
@@ -7948,10 +7952,10 @@
     </row>
     <row r="44">
       <c r="A44" t="s" s="2">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -7974,19 +7978,19 @@
         <v>92</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="N44" t="s" s="2">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="O44" t="s" s="2">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="P44" t="s" s="2">
         <v>81</v>
@@ -8035,7 +8039,7 @@
         <v>81</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>82</v>
@@ -8053,7 +8057,7 @@
         <v>81</v>
       </c>
       <c r="AL44" t="s" s="2">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="AM44" t="s" s="2">
         <v>81</v>
@@ -8062,24 +8066,24 @@
         <v>81</v>
       </c>
       <c r="AO44" t="s" s="2">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="AP44" t="s" s="2">
-        <v>81</v>
+        <v>384</v>
       </c>
       <c r="AQ44" t="s" s="2">
-        <v>383</v>
+        <v>81</v>
       </c>
       <c r="AR44" t="s" s="2">
-        <v>384</v>
+        <v>385</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="s" s="2">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -8105,20 +8109,20 @@
         <v>111</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="N45" s="2"/>
       <c r="O45" t="s" s="2">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="P45" t="s" s="2">
         <v>81</v>
       </c>
       <c r="Q45" t="s" s="2">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="R45" t="s" s="2">
         <v>81</v>
@@ -8142,10 +8146,10 @@
         <v>167</v>
       </c>
       <c r="Y45" t="s" s="2">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="Z45" t="s" s="2">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="AA45" t="s" s="2">
         <v>81</v>
@@ -8163,7 +8167,7 @@
         <v>81</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>82</v>
@@ -8181,7 +8185,7 @@
         <v>81</v>
       </c>
       <c r="AL45" t="s" s="2">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="AM45" t="s" s="2">
         <v>81</v>
@@ -8190,7 +8194,7 @@
         <v>81</v>
       </c>
       <c r="AO45" t="s" s="2">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="AP45" t="s" s="2">
         <v>81</v>
@@ -8204,10 +8208,10 @@
     </row>
     <row r="46">
       <c r="A46" t="s" s="2">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -8230,17 +8234,17 @@
         <v>92</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="N46" s="2"/>
       <c r="O46" t="s" s="2">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="P46" t="s" s="2">
         <v>81</v>
@@ -8289,7 +8293,7 @@
         <v>81</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>82</v>
@@ -8307,7 +8311,7 @@
         <v>81</v>
       </c>
       <c r="AL46" t="s" s="2">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="AM46" t="s" s="2">
         <v>81</v>
@@ -8316,7 +8320,7 @@
         <v>81</v>
       </c>
       <c r="AO46" t="s" s="2">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="AP46" t="s" s="2">
         <v>81</v>
@@ -8330,10 +8334,10 @@
     </row>
     <row r="47">
       <c r="A47" t="s" s="2">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -8359,14 +8363,14 @@
         <v>105</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="N47" s="2"/>
       <c r="O47" t="s" s="2">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="P47" t="s" s="2">
         <v>81</v>
@@ -8415,7 +8419,7 @@
         <v>81</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>82</v>
@@ -8424,7 +8428,7 @@
         <v>91</v>
       </c>
       <c r="AI47" t="s" s="2">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="AJ47" t="s" s="2">
         <v>103</v>
@@ -8433,7 +8437,7 @@
         <v>81</v>
       </c>
       <c r="AL47" t="s" s="2">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="AM47" t="s" s="2">
         <v>81</v>
@@ -8442,7 +8446,7 @@
         <v>81</v>
       </c>
       <c r="AO47" t="s" s="2">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="AP47" t="s" s="2">
         <v>81</v>
@@ -8456,10 +8460,10 @@
     </row>
     <row r="48">
       <c r="A48" t="s" s="2">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -8485,16 +8489,16 @@
         <v>111</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="N48" t="s" s="2">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="O48" t="s" s="2">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="P48" t="s" s="2">
         <v>81</v>
@@ -8543,7 +8547,7 @@
         <v>81</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>82</v>
@@ -8561,7 +8565,7 @@
         <v>81</v>
       </c>
       <c r="AL48" t="s" s="2">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="AM48" t="s" s="2">
         <v>81</v>
@@ -8570,7 +8574,7 @@
         <v>81</v>
       </c>
       <c r="AO48" t="s" s="2">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="AP48" t="s" s="2">
         <v>81</v>
@@ -8584,10 +8588,10 @@
     </row>
     <row r="49">
       <c r="A49" t="s" s="2">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -8610,13 +8614,13 @@
         <v>81</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="N49" s="2"/>
       <c r="O49" s="2"/>
@@ -8667,7 +8671,7 @@
         <v>81</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>82</v>
@@ -8685,7 +8689,7 @@
         <v>81</v>
       </c>
       <c r="AL49" t="s" s="2">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="AM49" t="s" s="2">
         <v>81</v>
@@ -8694,24 +8698,24 @@
         <v>81</v>
       </c>
       <c r="AO49" t="s" s="2">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="AP49" t="s" s="2">
-        <v>81</v>
+        <v>422</v>
       </c>
       <c r="AQ49" t="s" s="2">
-        <v>421</v>
+        <v>81</v>
       </c>
       <c r="AR49" t="s" s="2">
-        <v>422</v>
+        <v>423</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="s" s="2">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -8734,13 +8738,13 @@
         <v>92</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="N50" s="2"/>
       <c r="O50" s="2"/>
@@ -8791,7 +8795,7 @@
         <v>81</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>82</v>
@@ -8809,22 +8813,22 @@
         <v>81</v>
       </c>
       <c r="AL50" t="s" s="2">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="AM50" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN50" t="s" s="2">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="AO50" t="s" s="2">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="AP50" t="s" s="2">
-        <v>81</v>
+        <v>431</v>
       </c>
       <c r="AQ50" t="s" s="2">
-        <v>430</v>
+        <v>81</v>
       </c>
       <c r="AR50" t="s" s="2">
         <v>81</v>
@@ -8832,10 +8836,10 @@
     </row>
     <row r="51">
       <c r="A51" t="s" s="2">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -8858,13 +8862,13 @@
         <v>81</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="N51" s="2"/>
       <c r="O51" s="2"/>
@@ -8915,7 +8919,7 @@
         <v>81</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>82</v>
@@ -8930,25 +8934,25 @@
         <v>103</v>
       </c>
       <c r="AK51" t="s" s="2">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="AL51" t="s" s="2">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="AM51" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN51" t="s" s="2">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="AO51" t="s" s="2">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="AP51" t="s" s="2">
-        <v>81</v>
+        <v>437</v>
       </c>
       <c r="AQ51" t="s" s="2">
-        <v>436</v>
+        <v>81</v>
       </c>
       <c r="AR51" t="s" s="2">
         <v>81</v>
@@ -8956,10 +8960,10 @@
     </row>
     <row r="52">
       <c r="A52" t="s" s="2">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -8982,13 +8986,13 @@
         <v>81</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="N52" s="2"/>
       <c r="O52" s="2"/>
@@ -9039,7 +9043,7 @@
         <v>81</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>82</v>
@@ -9057,16 +9061,16 @@
         <v>81</v>
       </c>
       <c r="AL52" t="s" s="2">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="AM52" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN52" t="s" s="2">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="AO52" t="s" s="2">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="AP52" t="s" s="2">
         <v>81</v>
@@ -9080,10 +9084,10 @@
     </row>
     <row r="53">
       <c r="A53" t="s" s="2">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -9106,13 +9110,13 @@
         <v>81</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="N53" s="2"/>
       <c r="O53" s="2"/>
@@ -9163,7 +9167,7 @@
         <v>81</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>82</v>
@@ -9181,7 +9185,7 @@
         <v>81</v>
       </c>
       <c r="AL53" t="s" s="2">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="AM53" t="s" s="2">
         <v>81</v>
@@ -9204,10 +9208,10 @@
     </row>
     <row r="54">
       <c r="A54" t="s" s="2">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -9236,7 +9240,7 @@
         <v>138</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="N54" t="s" s="2">
         <v>140</v>
@@ -9277,19 +9281,19 @@
         <v>81</v>
       </c>
       <c r="AB54" t="s" s="2">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="AC54" t="s" s="2">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="AD54" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AE54" t="s" s="2">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>82</v>
@@ -9307,7 +9311,7 @@
         <v>81</v>
       </c>
       <c r="AL54" t="s" s="2">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="AM54" t="s" s="2">
         <v>81</v>
@@ -9330,10 +9334,10 @@
     </row>
     <row r="55">
       <c r="A55" t="s" s="2">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -9356,16 +9360,16 @@
         <v>92</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="N55" t="s" s="2">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="O55" s="2"/>
       <c r="P55" t="s" s="2">
@@ -9415,7 +9419,7 @@
         <v>81</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>82</v>
@@ -9424,7 +9428,7 @@
         <v>91</v>
       </c>
       <c r="AI55" t="s" s="2">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="AJ55" t="s" s="2">
         <v>103</v>
@@ -9456,10 +9460,10 @@
     </row>
     <row r="56">
       <c r="A56" t="s" s="2">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -9485,13 +9489,13 @@
         <v>105</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="N56" t="s" s="2">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="O56" s="2"/>
       <c r="P56" t="s" s="2">
@@ -9517,13 +9521,13 @@
         <v>81</v>
       </c>
       <c r="X56" t="s" s="2">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="Y56" t="s" s="2">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="Z56" t="s" s="2">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="AA56" t="s" s="2">
         <v>81</v>
@@ -9541,7 +9545,7 @@
         <v>81</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>82</v>
@@ -9582,10 +9586,10 @@
     </row>
     <row r="57">
       <c r="A57" t="s" s="2">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -9611,13 +9615,13 @@
         <v>149</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="N57" t="s" s="2">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="O57" s="2"/>
       <c r="P57" t="s" s="2">
@@ -9667,7 +9671,7 @@
         <v>81</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>82</v>
@@ -9685,7 +9689,7 @@
         <v>81</v>
       </c>
       <c r="AL57" t="s" s="2">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="AM57" t="s" s="2">
         <v>81</v>
@@ -9708,10 +9712,10 @@
     </row>
     <row r="58">
       <c r="A58" t="s" s="2">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -9734,16 +9738,16 @@
         <v>92</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="N58" t="s" s="2">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="O58" s="2"/>
       <c r="P58" t="s" s="2">
@@ -9793,7 +9797,7 @@
         <v>81</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>82</v>
@@ -9823,21 +9827,21 @@
         <v>81</v>
       </c>
       <c r="AP58" t="s" s="2">
-        <v>81</v>
+        <v>471</v>
       </c>
       <c r="AQ58" t="s" s="2">
-        <v>470</v>
+        <v>81</v>
       </c>
       <c r="AR58" t="s" s="2">
-        <v>471</v>
+        <v>472</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="s" s="2">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -9860,13 +9864,13 @@
         <v>81</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="N59" s="2"/>
       <c r="O59" s="2"/>
@@ -9917,7 +9921,7 @@
         <v>81</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>82</v>
@@ -9935,13 +9939,13 @@
         <v>81</v>
       </c>
       <c r="AL59" t="s" s="2">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="AM59" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN59" t="s" s="2">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="AO59" t="s" s="2">
         <v>81</v>
@@ -9958,10 +9962,10 @@
     </row>
     <row r="60">
       <c r="A60" t="s" s="2">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -9984,13 +9988,13 @@
         <v>81</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="N60" s="2"/>
       <c r="O60" s="2"/>
@@ -10041,7 +10045,7 @@
         <v>81</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>82</v>
@@ -10056,10 +10060,10 @@
         <v>103</v>
       </c>
       <c r="AK60" t="s" s="2">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="AL60" t="s" s="2">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="AM60" t="s" s="2">
         <v>81</v>
@@ -10068,7 +10072,7 @@
         <v>81</v>
       </c>
       <c r="AO60" t="s" s="2">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="AP60" t="s" s="2">
         <v>81</v>
@@ -10082,10 +10086,10 @@
     </row>
     <row r="61">
       <c r="A61" t="s" s="2">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -10108,16 +10112,16 @@
         <v>81</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="N61" t="s" s="2">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="O61" s="2"/>
       <c r="P61" t="s" s="2">
@@ -10167,7 +10171,7 @@
         <v>81</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>82</v>
@@ -10185,7 +10189,7 @@
         <v>81</v>
       </c>
       <c r="AL61" t="s" s="2">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="AM61" t="s" s="2">
         <v>81</v>
@@ -10208,10 +10212,10 @@
     </row>
     <row r="62">
       <c r="A62" t="s" s="2">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -10234,13 +10238,13 @@
         <v>81</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="N62" s="2"/>
       <c r="O62" s="2"/>
@@ -10291,7 +10295,7 @@
         <v>81</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>82</v>
@@ -10309,7 +10313,7 @@
         <v>81</v>
       </c>
       <c r="AL62" t="s" s="2">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="AM62" t="s" s="2">
         <v>81</v>
@@ -10332,10 +10336,10 @@
     </row>
     <row r="63">
       <c r="A63" t="s" s="2">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -10364,7 +10368,7 @@
         <v>138</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="N63" t="s" s="2">
         <v>140</v>
@@ -10405,19 +10409,19 @@
         <v>81</v>
       </c>
       <c r="AB63" t="s" s="2">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="AC63" t="s" s="2">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="AD63" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AE63" t="s" s="2">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>82</v>
@@ -10435,7 +10439,7 @@
         <v>81</v>
       </c>
       <c r="AL63" t="s" s="2">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="AM63" t="s" s="2">
         <v>81</v>
@@ -10458,14 +10462,14 @@
     </row>
     <row r="64">
       <c r="A64" t="s" s="2">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="E64" s="2"/>
       <c r="F64" t="s" s="2">
@@ -10487,10 +10491,10 @@
         <v>137</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="N64" t="s" s="2">
         <v>140</v>
@@ -10545,7 +10549,7 @@
         <v>81</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>82</v>
@@ -10586,10 +10590,10 @@
     </row>
     <row r="65">
       <c r="A65" t="s" s="2">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -10612,17 +10616,17 @@
         <v>92</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="N65" s="2"/>
       <c r="O65" t="s" s="2">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="P65" t="s" s="2">
         <v>81</v>
@@ -10671,7 +10675,7 @@
         <v>81</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>82</v>
@@ -10689,7 +10693,7 @@
         <v>81</v>
       </c>
       <c r="AL65" t="s" s="2">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="AM65" t="s" s="2">
         <v>81</v>
@@ -10698,7 +10702,7 @@
         <v>81</v>
       </c>
       <c r="AO65" t="s" s="2">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="AP65" t="s" s="2">
         <v>81</v>
@@ -10712,10 +10716,10 @@
     </row>
     <row r="66">
       <c r="A66" t="s" s="2">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -10738,17 +10742,17 @@
         <v>92</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="N66" s="2"/>
       <c r="O66" t="s" s="2">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="P66" t="s" s="2">
         <v>81</v>
@@ -10797,7 +10801,7 @@
         <v>81</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>82</v>
@@ -10815,7 +10819,7 @@
         <v>81</v>
       </c>
       <c r="AL66" t="s" s="2">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="AM66" t="s" s="2">
         <v>81</v>
@@ -10824,24 +10828,24 @@
         <v>81</v>
       </c>
       <c r="AO66" t="s" s="2">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="AP66" t="s" s="2">
-        <v>81</v>
+        <v>509</v>
       </c>
       <c r="AQ66" t="s" s="2">
-        <v>508</v>
+        <v>81</v>
       </c>
       <c r="AR66" t="s" s="2">
-        <v>509</v>
+        <v>510</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="s" s="2">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -10864,19 +10868,19 @@
         <v>92</v>
       </c>
       <c r="K67" t="s" s="2">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="N67" t="s" s="2">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="O67" t="s" s="2">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="P67" t="s" s="2">
         <v>81</v>
@@ -10901,13 +10905,13 @@
         <v>81</v>
       </c>
       <c r="X67" t="s" s="2">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="Y67" t="s" s="2">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="Z67" t="s" s="2">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="AA67" t="s" s="2">
         <v>81</v>
@@ -10925,7 +10929,7 @@
         <v>81</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>82</v>
@@ -10943,7 +10947,7 @@
         <v>81</v>
       </c>
       <c r="AL67" t="s" s="2">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="AM67" t="s" s="2">
         <v>81</v>
@@ -10952,7 +10956,7 @@
         <v>81</v>
       </c>
       <c r="AO67" t="s" s="2">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="AP67" t="s" s="2">
         <v>81</v>
@@ -10966,10 +10970,10 @@
     </row>
     <row r="68">
       <c r="A68" t="s" s="2">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -10992,13 +10996,13 @@
         <v>92</v>
       </c>
       <c r="K68" t="s" s="2">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="N68" s="2"/>
       <c r="O68" s="2"/>
@@ -11049,7 +11053,7 @@
         <v>81</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>82</v>
@@ -11067,7 +11071,7 @@
         <v>81</v>
       </c>
       <c r="AL68" t="s" s="2">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="AM68" t="s" s="2">
         <v>81</v>
@@ -11076,13 +11080,13 @@
         <v>81</v>
       </c>
       <c r="AO68" t="s" s="2">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="AP68" t="s" s="2">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="AQ68" t="s" s="2">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="AR68" t="s" s="2">
         <v>81</v>
@@ -11090,10 +11094,10 @@
     </row>
     <row r="69">
       <c r="A69" t="s" s="2">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -11116,19 +11120,19 @@
         <v>92</v>
       </c>
       <c r="K69" t="s" s="2">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="N69" t="s" s="2">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="O69" t="s" s="2">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="P69" t="s" s="2">
         <v>81</v>
@@ -11177,7 +11181,7 @@
         <v>81</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>82</v>
@@ -11195,7 +11199,7 @@
         <v>81</v>
       </c>
       <c r="AL69" t="s" s="2">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="AM69" t="s" s="2">
         <v>81</v>
@@ -11218,10 +11222,10 @@
     </row>
     <row r="70">
       <c r="A70" t="s" s="2">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -11244,16 +11248,16 @@
         <v>92</v>
       </c>
       <c r="K70" t="s" s="2">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="N70" t="s" s="2">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="O70" s="2"/>
       <c r="P70" t="s" s="2">
@@ -11279,13 +11283,13 @@
         <v>81</v>
       </c>
       <c r="X70" t="s" s="2">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="Y70" t="s" s="2">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="Z70" t="s" s="2">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="AA70" t="s" s="2">
         <v>81</v>
@@ -11303,7 +11307,7 @@
         <v>81</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>82</v>
@@ -11321,7 +11325,7 @@
         <v>81</v>
       </c>
       <c r="AL70" t="s" s="2">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="AM70" t="s" s="2">
         <v>81</v>
@@ -11330,7 +11334,7 @@
         <v>81</v>
       </c>
       <c r="AO70" t="s" s="2">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="AP70" t="s" s="2">
         <v>81</v>
@@ -11344,10 +11348,10 @@
     </row>
     <row r="71">
       <c r="A71" t="s" s="2">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -11370,19 +11374,19 @@
         <v>92</v>
       </c>
       <c r="K71" t="s" s="2">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="N71" t="s" s="2">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="O71" t="s" s="2">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="P71" t="s" s="2">
         <v>81</v>
@@ -11407,13 +11411,13 @@
         <v>81</v>
       </c>
       <c r="X71" t="s" s="2">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="Y71" t="s" s="2">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="Z71" t="s" s="2">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="AA71" t="s" s="2">
         <v>81</v>
@@ -11431,7 +11435,7 @@
         <v>81</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>82</v>
@@ -11449,7 +11453,7 @@
         <v>81</v>
       </c>
       <c r="AL71" t="s" s="2">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="AM71" t="s" s="2">
         <v>81</v>
@@ -11458,7 +11462,7 @@
         <v>81</v>
       </c>
       <c r="AO71" t="s" s="2">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="AP71" t="s" s="2">
         <v>81</v>
@@ -11472,10 +11476,10 @@
     </row>
     <row r="72">
       <c r="A72" t="s" s="2">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -11498,17 +11502,17 @@
         <v>92</v>
       </c>
       <c r="K72" t="s" s="2">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="N72" s="2"/>
       <c r="O72" t="s" s="2">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="P72" t="s" s="2">
         <v>81</v>
@@ -11533,13 +11537,13 @@
         <v>81</v>
       </c>
       <c r="X72" t="s" s="2">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="Y72" t="s" s="2">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="Z72" t="s" s="2">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="AA72" t="s" s="2">
         <v>81</v>
@@ -11557,7 +11561,7 @@
         <v>81</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>82</v>
@@ -11575,7 +11579,7 @@
         <v>81</v>
       </c>
       <c r="AL72" t="s" s="2">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="AM72" t="s" s="2">
         <v>81</v>
@@ -11584,7 +11588,7 @@
         <v>81</v>
       </c>
       <c r="AO72" t="s" s="2">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="AP72" t="s" s="2">
         <v>81</v>
@@ -11598,10 +11602,10 @@
     </row>
     <row r="73">
       <c r="A73" t="s" s="2">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -11624,19 +11628,19 @@
         <v>92</v>
       </c>
       <c r="K73" t="s" s="2">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="L73" t="s" s="2">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="M73" t="s" s="2">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="N73" t="s" s="2">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="O73" t="s" s="2">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="P73" t="s" s="2">
         <v>81</v>
@@ -11661,13 +11665,13 @@
         <v>81</v>
       </c>
       <c r="X73" t="s" s="2">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="Y73" t="s" s="2">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="Z73" t="s" s="2">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="AA73" t="s" s="2">
         <v>81</v>
@@ -11685,7 +11689,7 @@
         <v>81</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>82</v>
@@ -11703,7 +11707,7 @@
         <v>81</v>
       </c>
       <c r="AL73" t="s" s="2">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="AM73" t="s" s="2">
         <v>81</v>
@@ -11712,7 +11716,7 @@
         <v>81</v>
       </c>
       <c r="AO73" t="s" s="2">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="AP73" t="s" s="2">
         <v>81</v>
@@ -11726,10 +11730,10 @@
     </row>
     <row r="74">
       <c r="A74" t="s" s="2">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -11752,13 +11756,13 @@
         <v>92</v>
       </c>
       <c r="K74" t="s" s="2">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="L74" t="s" s="2">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="M74" t="s" s="2">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="N74" s="2"/>
       <c r="O74" s="2"/>
@@ -11809,7 +11813,7 @@
         <v>81</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>82</v>
@@ -11836,7 +11840,7 @@
         <v>81</v>
       </c>
       <c r="AO74" t="s" s="2">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="AP74" t="s" s="2">
         <v>81</v>
@@ -11850,10 +11854,10 @@
     </row>
     <row r="75">
       <c r="A75" t="s" s="2">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -11876,13 +11880,13 @@
         <v>81</v>
       </c>
       <c r="K75" t="s" s="2">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="L75" t="s" s="2">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="M75" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="N75" s="2"/>
       <c r="O75" s="2"/>
@@ -11933,7 +11937,7 @@
         <v>81</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>82</v>
@@ -11951,7 +11955,7 @@
         <v>81</v>
       </c>
       <c r="AL75" t="s" s="2">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="AM75" t="s" s="2">
         <v>81</v>
@@ -11974,10 +11978,10 @@
     </row>
     <row r="76">
       <c r="A76" t="s" s="2">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -12006,7 +12010,7 @@
         <v>138</v>
       </c>
       <c r="M76" t="s" s="2">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="N76" t="s" s="2">
         <v>140</v>
@@ -12047,19 +12051,19 @@
         <v>81</v>
       </c>
       <c r="AB76" t="s" s="2">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="AC76" t="s" s="2">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="AD76" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AE76" t="s" s="2">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>82</v>
@@ -12077,7 +12081,7 @@
         <v>81</v>
       </c>
       <c r="AL76" t="s" s="2">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="AM76" t="s" s="2">
         <v>81</v>
@@ -12100,10 +12104,10 @@
     </row>
     <row r="77">
       <c r="A77" t="s" s="2">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
@@ -12126,17 +12130,17 @@
         <v>92</v>
       </c>
       <c r="K77" t="s" s="2">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="L77" t="s" s="2">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="M77" t="s" s="2">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="N77" s="2"/>
       <c r="O77" t="s" s="2">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="P77" t="s" s="2">
         <v>81</v>
@@ -12161,13 +12165,13 @@
         <v>81</v>
       </c>
       <c r="X77" t="s" s="2">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="Y77" t="s" s="2">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="Z77" t="s" s="2">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="AA77" t="s" s="2">
         <v>81</v>
@@ -12185,7 +12189,7 @@
         <v>81</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>82</v>
@@ -12212,7 +12216,7 @@
         <v>81</v>
       </c>
       <c r="AO77" t="s" s="2">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="AP77" t="s" s="2">
         <v>81</v>
@@ -12226,10 +12230,10 @@
     </row>
     <row r="78">
       <c r="A78" t="s" s="2">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -12252,19 +12256,19 @@
         <v>92</v>
       </c>
       <c r="K78" t="s" s="2">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="L78" t="s" s="2">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="M78" t="s" s="2">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="N78" t="s" s="2">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="O78" t="s" s="2">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="P78" t="s" s="2">
         <v>81</v>
@@ -12301,17 +12305,17 @@
         <v>81</v>
       </c>
       <c r="AB78" t="s" s="2">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="AC78" s="2"/>
       <c r="AD78" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AE78" t="s" s="2">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>82</v>
@@ -12329,7 +12333,7 @@
         <v>81</v>
       </c>
       <c r="AL78" t="s" s="2">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="AM78" t="s" s="2">
         <v>81</v>
@@ -12338,7 +12342,7 @@
         <v>81</v>
       </c>
       <c r="AO78" t="s" s="2">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="AP78" t="s" s="2">
         <v>81</v>
@@ -12352,13 +12356,13 @@
     </row>
     <row r="79">
       <c r="A79" t="s" s="2">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="C79" t="s" s="2">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="D79" t="s" s="2">
         <v>81</v>
@@ -12380,19 +12384,19 @@
         <v>81</v>
       </c>
       <c r="K79" t="s" s="2">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="L79" t="s" s="2">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="M79" t="s" s="2">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="N79" t="s" s="2">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="O79" t="s" s="2">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="P79" t="s" s="2">
         <v>81</v>
@@ -12441,7 +12445,7 @@
         <v>81</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="AG79" t="s" s="2">
         <v>82</v>
@@ -12450,16 +12454,16 @@
         <v>91</v>
       </c>
       <c r="AI79" t="s" s="2">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="AJ79" t="s" s="2">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="AK79" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AL79" t="s" s="2">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="AM79" t="s" s="2">
         <v>81</v>
@@ -12468,7 +12472,7 @@
         <v>81</v>
       </c>
       <c r="AO79" t="s" s="2">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="AP79" t="s" s="2">
         <v>81</v>
@@ -12482,10 +12486,10 @@
     </row>
     <row r="80">
       <c r="A80" t="s" s="2">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
@@ -12508,13 +12512,13 @@
         <v>81</v>
       </c>
       <c r="K80" t="s" s="2">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="L80" t="s" s="2">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="M80" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="N80" s="2"/>
       <c r="O80" s="2"/>
@@ -12565,7 +12569,7 @@
         <v>81</v>
       </c>
       <c r="AF80" t="s" s="2">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="AG80" t="s" s="2">
         <v>82</v>
@@ -12583,7 +12587,7 @@
         <v>81</v>
       </c>
       <c r="AL80" t="s" s="2">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="AM80" t="s" s="2">
         <v>81</v>
@@ -12606,10 +12610,10 @@
     </row>
     <row r="81">
       <c r="A81" t="s" s="2">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
@@ -12638,7 +12642,7 @@
         <v>138</v>
       </c>
       <c r="M81" t="s" s="2">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="N81" t="s" s="2">
         <v>140</v>
@@ -12679,19 +12683,19 @@
         <v>81</v>
       </c>
       <c r="AB81" t="s" s="2">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="AC81" t="s" s="2">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="AD81" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AE81" t="s" s="2">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="AF81" t="s" s="2">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="AG81" t="s" s="2">
         <v>82</v>
@@ -12709,7 +12713,7 @@
         <v>81</v>
       </c>
       <c r="AL81" t="s" s="2">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="AM81" t="s" s="2">
         <v>81</v>
@@ -12732,10 +12736,10 @@
     </row>
     <row r="82">
       <c r="A82" t="s" s="2">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
@@ -12758,19 +12762,19 @@
         <v>92</v>
       </c>
       <c r="K82" t="s" s="2">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="L82" t="s" s="2">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="M82" t="s" s="2">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="N82" t="s" s="2">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="O82" t="s" s="2">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="P82" t="s" s="2">
         <v>81</v>
@@ -12819,7 +12823,7 @@
         <v>81</v>
       </c>
       <c r="AF82" t="s" s="2">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="AG82" t="s" s="2">
         <v>82</v>
@@ -12837,7 +12841,7 @@
         <v>81</v>
       </c>
       <c r="AL82" t="s" s="2">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="AM82" t="s" s="2">
         <v>81</v>
@@ -12846,24 +12850,24 @@
         <v>81</v>
       </c>
       <c r="AO82" t="s" s="2">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="AP82" t="s" s="2">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="AQ82" t="s" s="2">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="AR82" t="s" s="2">
-        <v>613</v>
+        <v>614</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="s" s="2">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
@@ -12889,20 +12893,20 @@
         <v>111</v>
       </c>
       <c r="L83" t="s" s="2">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="M83" t="s" s="2">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="N83" s="2"/>
       <c r="O83" t="s" s="2">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="P83" t="s" s="2">
         <v>81</v>
       </c>
       <c r="Q83" t="s" s="2">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="R83" t="s" s="2">
         <v>81</v>
@@ -12926,10 +12930,10 @@
         <v>167</v>
       </c>
       <c r="Y83" t="s" s="2">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="Z83" t="s" s="2">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="AA83" t="s" s="2">
         <v>81</v>
@@ -12947,7 +12951,7 @@
         <v>81</v>
       </c>
       <c r="AF83" t="s" s="2">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="AG83" t="s" s="2">
         <v>82</v>
@@ -12965,7 +12969,7 @@
         <v>81</v>
       </c>
       <c r="AL83" t="s" s="2">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="AM83" t="s" s="2">
         <v>81</v>
@@ -12974,7 +12978,7 @@
         <v>81</v>
       </c>
       <c r="AO83" t="s" s="2">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="AP83" t="s" s="2">
         <v>81</v>
@@ -12988,10 +12992,10 @@
     </row>
     <row r="84">
       <c r="A84" t="s" s="2">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
@@ -13014,17 +13018,17 @@
         <v>92</v>
       </c>
       <c r="K84" t="s" s="2">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="L84" t="s" s="2">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="M84" t="s" s="2">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="N84" s="2"/>
       <c r="O84" t="s" s="2">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="P84" t="s" s="2">
         <v>81</v>
@@ -13073,7 +13077,7 @@
         <v>81</v>
       </c>
       <c r="AF84" t="s" s="2">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="AG84" t="s" s="2">
         <v>82</v>
@@ -13091,7 +13095,7 @@
         <v>81</v>
       </c>
       <c r="AL84" t="s" s="2">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="AM84" t="s" s="2">
         <v>81</v>
@@ -13100,24 +13104,24 @@
         <v>81</v>
       </c>
       <c r="AO84" t="s" s="2">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="AP84" t="s" s="2">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="AQ84" t="s" s="2">
-        <v>619</v>
+        <v>620</v>
       </c>
       <c r="AR84" t="s" s="2">
-        <v>620</v>
+        <v>621</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="s" s="2">
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>622</v>
+        <v>623</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
@@ -13143,14 +13147,14 @@
         <v>105</v>
       </c>
       <c r="L85" t="s" s="2">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="M85" t="s" s="2">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="N85" s="2"/>
       <c r="O85" t="s" s="2">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="P85" t="s" s="2">
         <v>81</v>
@@ -13199,7 +13203,7 @@
         <v>81</v>
       </c>
       <c r="AF85" t="s" s="2">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="AG85" t="s" s="2">
         <v>82</v>
@@ -13208,7 +13212,7 @@
         <v>91</v>
       </c>
       <c r="AI85" t="s" s="2">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="AJ85" t="s" s="2">
         <v>103</v>
@@ -13217,7 +13221,7 @@
         <v>81</v>
       </c>
       <c r="AL85" t="s" s="2">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="AM85" t="s" s="2">
         <v>81</v>
@@ -13226,7 +13230,7 @@
         <v>81</v>
       </c>
       <c r="AO85" t="s" s="2">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="AP85" t="s" s="2">
         <v>81</v>
@@ -13240,10 +13244,10 @@
     </row>
     <row r="86">
       <c r="A86" t="s" s="2">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
@@ -13269,16 +13273,16 @@
         <v>111</v>
       </c>
       <c r="L86" t="s" s="2">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="M86" t="s" s="2">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="N86" t="s" s="2">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="O86" t="s" s="2">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="P86" t="s" s="2">
         <v>81</v>
@@ -13327,7 +13331,7 @@
         <v>81</v>
       </c>
       <c r="AF86" t="s" s="2">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="AG86" t="s" s="2">
         <v>82</v>
@@ -13345,7 +13349,7 @@
         <v>81</v>
       </c>
       <c r="AL86" t="s" s="2">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="AM86" t="s" s="2">
         <v>81</v>
@@ -13354,24 +13358,24 @@
         <v>81</v>
       </c>
       <c r="AO86" t="s" s="2">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="AP86" t="s" s="2">
-        <v>618</v>
+        <v>626</v>
       </c>
       <c r="AQ86" t="s" s="2">
-        <v>625</v>
+        <v>620</v>
       </c>
       <c r="AR86" t="s" s="2">
-        <v>620</v>
+        <v>621</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="s" s="2">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
@@ -13394,19 +13398,19 @@
         <v>92</v>
       </c>
       <c r="K87" t="s" s="2">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="L87" t="s" s="2">
-        <v>628</v>
+        <v>629</v>
       </c>
       <c r="M87" t="s" s="2">
-        <v>629</v>
+        <v>630</v>
       </c>
       <c r="N87" t="s" s="2">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="O87" t="s" s="2">
-        <v>631</v>
+        <v>632</v>
       </c>
       <c r="P87" t="s" s="2">
         <v>81</v>
@@ -13455,7 +13459,7 @@
         <v>81</v>
       </c>
       <c r="AF87" t="s" s="2">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="AG87" t="s" s="2">
         <v>82</v>
@@ -13473,7 +13477,7 @@
         <v>81</v>
       </c>
       <c r="AL87" t="s" s="2">
-        <v>633</v>
+        <v>634</v>
       </c>
       <c r="AM87" t="s" s="2">
         <v>81</v>
@@ -13482,7 +13486,7 @@
         <v>81</v>
       </c>
       <c r="AO87" t="s" s="2">
-        <v>634</v>
+        <v>635</v>
       </c>
       <c r="AP87" t="s" s="2">
         <v>81</v>
@@ -13496,10 +13500,10 @@
     </row>
     <row r="88">
       <c r="A88" t="s" s="2">
-        <v>635</v>
+        <v>636</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>635</v>
+        <v>636</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
@@ -13522,19 +13526,19 @@
         <v>92</v>
       </c>
       <c r="K88" t="s" s="2">
-        <v>636</v>
+        <v>637</v>
       </c>
       <c r="L88" t="s" s="2">
-        <v>637</v>
+        <v>638</v>
       </c>
       <c r="M88" t="s" s="2">
-        <v>638</v>
+        <v>639</v>
       </c>
       <c r="N88" t="s" s="2">
-        <v>639</v>
+        <v>640</v>
       </c>
       <c r="O88" t="s" s="2">
-        <v>640</v>
+        <v>641</v>
       </c>
       <c r="P88" t="s" s="2">
         <v>81</v>
@@ -13583,7 +13587,7 @@
         <v>81</v>
       </c>
       <c r="AF88" t="s" s="2">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="AG88" t="s" s="2">
         <v>82</v>
@@ -13601,7 +13605,7 @@
         <v>81</v>
       </c>
       <c r="AL88" t="s" s="2">
-        <v>642</v>
+        <v>643</v>
       </c>
       <c r="AM88" t="s" s="2">
         <v>81</v>
@@ -13610,7 +13614,7 @@
         <v>81</v>
       </c>
       <c r="AO88" t="s" s="2">
-        <v>643</v>
+        <v>644</v>
       </c>
       <c r="AP88" t="s" s="2">
         <v>81</v>
@@ -13624,10 +13628,10 @@
     </row>
     <row r="89">
       <c r="A89" t="s" s="2">
-        <v>644</v>
+        <v>645</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>644</v>
+        <v>645</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
@@ -13650,19 +13654,19 @@
         <v>92</v>
       </c>
       <c r="K89" t="s" s="2">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="L89" t="s" s="2">
-        <v>645</v>
+        <v>646</v>
       </c>
       <c r="M89" t="s" s="2">
-        <v>646</v>
+        <v>647</v>
       </c>
       <c r="N89" t="s" s="2">
-        <v>647</v>
+        <v>648</v>
       </c>
       <c r="O89" t="s" s="2">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="P89" t="s" s="2">
         <v>81</v>
@@ -13711,7 +13715,7 @@
         <v>81</v>
       </c>
       <c r="AF89" t="s" s="2">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="AG89" t="s" s="2">
         <v>82</v>
@@ -13729,7 +13733,7 @@
         <v>81</v>
       </c>
       <c r="AL89" t="s" s="2">
-        <v>650</v>
+        <v>651</v>
       </c>
       <c r="AM89" t="s" s="2">
         <v>81</v>
@@ -13752,10 +13756,10 @@
     </row>
     <row r="90">
       <c r="A90" t="s" s="2">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
@@ -13778,17 +13782,17 @@
         <v>92</v>
       </c>
       <c r="K90" t="s" s="2">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="L90" t="s" s="2">
-        <v>652</v>
+        <v>653</v>
       </c>
       <c r="M90" t="s" s="2">
-        <v>653</v>
+        <v>654</v>
       </c>
       <c r="N90" s="2"/>
       <c r="O90" t="s" s="2">
-        <v>654</v>
+        <v>655</v>
       </c>
       <c r="P90" t="s" s="2">
         <v>81</v>
@@ -13837,7 +13841,7 @@
         <v>81</v>
       </c>
       <c r="AF90" t="s" s="2">
-        <v>655</v>
+        <v>656</v>
       </c>
       <c r="AG90" t="s" s="2">
         <v>82</v>
@@ -13855,7 +13859,7 @@
         <v>81</v>
       </c>
       <c r="AL90" t="s" s="2">
-        <v>650</v>
+        <v>651</v>
       </c>
       <c r="AM90" t="s" s="2">
         <v>81</v>
@@ -13878,10 +13882,10 @@
     </row>
     <row r="91">
       <c r="A91" t="s" s="2">
-        <v>656</v>
+        <v>657</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>656</v>
+        <v>657</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
@@ -13904,13 +13908,13 @@
         <v>81</v>
       </c>
       <c r="K91" t="s" s="2">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="L91" t="s" s="2">
-        <v>657</v>
+        <v>658</v>
       </c>
       <c r="M91" t="s" s="2">
-        <v>658</v>
+        <v>659</v>
       </c>
       <c r="N91" s="2"/>
       <c r="O91" s="2"/>
@@ -13961,7 +13965,7 @@
         <v>81</v>
       </c>
       <c r="AF91" t="s" s="2">
-        <v>656</v>
+        <v>657</v>
       </c>
       <c r="AG91" t="s" s="2">
         <v>82</v>
@@ -13979,13 +13983,13 @@
         <v>81</v>
       </c>
       <c r="AL91" t="s" s="2">
-        <v>659</v>
+        <v>660</v>
       </c>
       <c r="AM91" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN91" t="s" s="2">
-        <v>660</v>
+        <v>661</v>
       </c>
       <c r="AO91" t="s" s="2">
         <v>81</v>
@@ -14002,10 +14006,10 @@
     </row>
     <row r="92">
       <c r="A92" t="s" s="2">
-        <v>661</v>
+        <v>662</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>661</v>
+        <v>662</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
@@ -14028,13 +14032,13 @@
         <v>81</v>
       </c>
       <c r="K92" t="s" s="2">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="L92" t="s" s="2">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="M92" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="N92" s="2"/>
       <c r="O92" s="2"/>
@@ -14085,7 +14089,7 @@
         <v>81</v>
       </c>
       <c r="AF92" t="s" s="2">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="AG92" t="s" s="2">
         <v>82</v>
@@ -14103,7 +14107,7 @@
         <v>81</v>
       </c>
       <c r="AL92" t="s" s="2">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="AM92" t="s" s="2">
         <v>81</v>
@@ -14126,10 +14130,10 @@
     </row>
     <row r="93">
       <c r="A93" t="s" s="2">
-        <v>662</v>
+        <v>663</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>662</v>
+        <v>663</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
@@ -14158,7 +14162,7 @@
         <v>138</v>
       </c>
       <c r="M93" t="s" s="2">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="N93" t="s" s="2">
         <v>140</v>
@@ -14211,7 +14215,7 @@
         <v>81</v>
       </c>
       <c r="AF93" t="s" s="2">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="AG93" t="s" s="2">
         <v>82</v>
@@ -14229,7 +14233,7 @@
         <v>81</v>
       </c>
       <c r="AL93" t="s" s="2">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="AM93" t="s" s="2">
         <v>81</v>
@@ -14252,14 +14256,14 @@
     </row>
     <row r="94">
       <c r="A94" t="s" s="2">
-        <v>663</v>
+        <v>664</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>663</v>
+        <v>664</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" t="s" s="2">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="E94" s="2"/>
       <c r="F94" t="s" s="2">
@@ -14281,10 +14285,10 @@
         <v>137</v>
       </c>
       <c r="L94" t="s" s="2">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="M94" t="s" s="2">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="N94" t="s" s="2">
         <v>140</v>
@@ -14339,7 +14343,7 @@
         <v>81</v>
       </c>
       <c r="AF94" t="s" s="2">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="AG94" t="s" s="2">
         <v>82</v>
@@ -14380,10 +14384,10 @@
     </row>
     <row r="95">
       <c r="A95" t="s" s="2">
-        <v>664</v>
+        <v>665</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>664</v>
+        <v>665</v>
       </c>
       <c r="C95" s="2"/>
       <c r="D95" t="s" s="2">
@@ -14406,13 +14410,13 @@
         <v>81</v>
       </c>
       <c r="K95" t="s" s="2">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="L95" t="s" s="2">
-        <v>665</v>
+        <v>666</v>
       </c>
       <c r="M95" t="s" s="2">
-        <v>666</v>
+        <v>667</v>
       </c>
       <c r="N95" s="2"/>
       <c r="O95" s="2"/>
@@ -14463,7 +14467,7 @@
         <v>81</v>
       </c>
       <c r="AF95" t="s" s="2">
-        <v>664</v>
+        <v>665</v>
       </c>
       <c r="AG95" t="s" s="2">
         <v>91</v>
@@ -14481,7 +14485,7 @@
         <v>81</v>
       </c>
       <c r="AL95" t="s" s="2">
-        <v>667</v>
+        <v>668</v>
       </c>
       <c r="AM95" t="s" s="2">
         <v>81</v>
@@ -14504,10 +14508,10 @@
     </row>
     <row r="96">
       <c r="A96" t="s" s="2">
-        <v>668</v>
+        <v>669</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>668</v>
+        <v>669</v>
       </c>
       <c r="C96" s="2"/>
       <c r="D96" t="s" s="2">
@@ -14530,13 +14534,13 @@
         <v>81</v>
       </c>
       <c r="K96" t="s" s="2">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="L96" t="s" s="2">
-        <v>669</v>
+        <v>670</v>
       </c>
       <c r="M96" t="s" s="2">
-        <v>670</v>
+        <v>671</v>
       </c>
       <c r="N96" s="2"/>
       <c r="O96" s="2"/>
@@ -14563,13 +14567,13 @@
         <v>81</v>
       </c>
       <c r="X96" t="s" s="2">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="Y96" t="s" s="2">
-        <v>671</v>
+        <v>672</v>
       </c>
       <c r="Z96" t="s" s="2">
-        <v>672</v>
+        <v>673</v>
       </c>
       <c r="AA96" t="s" s="2">
         <v>81</v>
@@ -14587,7 +14591,7 @@
         <v>81</v>
       </c>
       <c r="AF96" t="s" s="2">
-        <v>668</v>
+        <v>669</v>
       </c>
       <c r="AG96" t="s" s="2">
         <v>82</v>
@@ -14605,16 +14609,16 @@
         <v>81</v>
       </c>
       <c r="AL96" t="s" s="2">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="AM96" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN96" t="s" s="2">
-        <v>673</v>
+        <v>674</v>
       </c>
       <c r="AO96" t="s" s="2">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="AP96" t="s" s="2">
         <v>81</v>
@@ -14628,10 +14632,10 @@
     </row>
     <row r="97">
       <c r="A97" t="s" s="2">
-        <v>675</v>
+        <v>676</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>675</v>
+        <v>676</v>
       </c>
       <c r="C97" s="2"/>
       <c r="D97" t="s" s="2">
@@ -14654,13 +14658,13 @@
         <v>81</v>
       </c>
       <c r="K97" t="s" s="2">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="L97" t="s" s="2">
-        <v>676</v>
+        <v>677</v>
       </c>
       <c r="M97" t="s" s="2">
-        <v>677</v>
+        <v>678</v>
       </c>
       <c r="N97" s="2"/>
       <c r="O97" s="2"/>
@@ -14687,13 +14691,13 @@
         <v>81</v>
       </c>
       <c r="X97" t="s" s="2">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="Y97" t="s" s="2">
-        <v>678</v>
+        <v>679</v>
       </c>
       <c r="Z97" t="s" s="2">
-        <v>679</v>
+        <v>680</v>
       </c>
       <c r="AA97" t="s" s="2">
         <v>81</v>
@@ -14711,7 +14715,7 @@
         <v>81</v>
       </c>
       <c r="AF97" t="s" s="2">
-        <v>675</v>
+        <v>676</v>
       </c>
       <c r="AG97" t="s" s="2">
         <v>82</v>
@@ -14729,13 +14733,13 @@
         <v>81</v>
       </c>
       <c r="AL97" t="s" s="2">
-        <v>680</v>
+        <v>681</v>
       </c>
       <c r="AM97" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN97" t="s" s="2">
-        <v>681</v>
+        <v>682</v>
       </c>
       <c r="AO97" t="s" s="2">
         <v>81</v>
@@ -14752,10 +14756,10 @@
     </row>
     <row r="98">
       <c r="A98" t="s" s="2">
-        <v>682</v>
+        <v>683</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>682</v>
+        <v>683</v>
       </c>
       <c r="C98" s="2"/>
       <c r="D98" t="s" s="2">
@@ -14778,13 +14782,13 @@
         <v>81</v>
       </c>
       <c r="K98" t="s" s="2">
-        <v>683</v>
+        <v>684</v>
       </c>
       <c r="L98" t="s" s="2">
-        <v>684</v>
+        <v>685</v>
       </c>
       <c r="M98" t="s" s="2">
-        <v>685</v>
+        <v>686</v>
       </c>
       <c r="N98" s="2"/>
       <c r="O98" s="2"/>
@@ -14835,7 +14839,7 @@
         <v>81</v>
       </c>
       <c r="AF98" t="s" s="2">
-        <v>682</v>
+        <v>683</v>
       </c>
       <c r="AG98" t="s" s="2">
         <v>82</v>
@@ -14853,13 +14857,13 @@
         <v>81</v>
       </c>
       <c r="AL98" t="s" s="2">
-        <v>686</v>
+        <v>687</v>
       </c>
       <c r="AM98" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN98" t="s" s="2">
-        <v>687</v>
+        <v>688</v>
       </c>
       <c r="AO98" t="s" s="2">
         <v>81</v>
@@ -14876,14 +14880,14 @@
     </row>
     <row r="99">
       <c r="A99" t="s" s="2">
-        <v>688</v>
+        <v>689</v>
       </c>
       <c r="B99" t="s" s="2">
-        <v>688</v>
+        <v>689</v>
       </c>
       <c r="C99" s="2"/>
       <c r="D99" t="s" s="2">
-        <v>689</v>
+        <v>690</v>
       </c>
       <c r="E99" s="2"/>
       <c r="F99" t="s" s="2">
@@ -14902,16 +14906,16 @@
         <v>81</v>
       </c>
       <c r="K99" t="s" s="2">
-        <v>690</v>
+        <v>691</v>
       </c>
       <c r="L99" t="s" s="2">
-        <v>691</v>
+        <v>692</v>
       </c>
       <c r="M99" t="s" s="2">
-        <v>692</v>
+        <v>693</v>
       </c>
       <c r="N99" t="s" s="2">
-        <v>693</v>
+        <v>694</v>
       </c>
       <c r="O99" s="2"/>
       <c r="P99" t="s" s="2">
@@ -14961,7 +14965,7 @@
         <v>81</v>
       </c>
       <c r="AF99" t="s" s="2">
-        <v>688</v>
+        <v>689</v>
       </c>
       <c r="AG99" t="s" s="2">
         <v>82</v>
@@ -14979,7 +14983,7 @@
         <v>81</v>
       </c>
       <c r="AL99" t="s" s="2">
-        <v>694</v>
+        <v>695</v>
       </c>
       <c r="AM99" t="s" s="2">
         <v>81</v>
@@ -15002,10 +15006,10 @@
     </row>
     <row r="100">
       <c r="A100" t="s" s="2">
-        <v>695</v>
+        <v>696</v>
       </c>
       <c r="B100" t="s" s="2">
-        <v>695</v>
+        <v>696</v>
       </c>
       <c r="C100" s="2"/>
       <c r="D100" t="s" s="2">
@@ -15028,16 +15032,16 @@
         <v>81</v>
       </c>
       <c r="K100" t="s" s="2">
-        <v>696</v>
+        <v>697</v>
       </c>
       <c r="L100" t="s" s="2">
-        <v>697</v>
+        <v>698</v>
       </c>
       <c r="M100" t="s" s="2">
-        <v>698</v>
+        <v>699</v>
       </c>
       <c r="N100" t="s" s="2">
-        <v>699</v>
+        <v>700</v>
       </c>
       <c r="O100" s="2"/>
       <c r="P100" t="s" s="2">
@@ -15087,7 +15091,7 @@
         <v>81</v>
       </c>
       <c r="AF100" t="s" s="2">
-        <v>695</v>
+        <v>696</v>
       </c>
       <c r="AG100" t="s" s="2">
         <v>82</v>
@@ -15105,7 +15109,7 @@
         <v>81</v>
       </c>
       <c r="AL100" t="s" s="2">
-        <v>700</v>
+        <v>701</v>
       </c>
       <c r="AM100" t="s" s="2">
         <v>81</v>

--- a/docs/StructureDefinition-MedDispenseRefillMedicationDispense.xlsx
+++ b/docs/StructureDefinition-MedDispenseRefillMedicationDispense.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.4.0</t>
+    <t>0.5.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-11-15T12:04:59+00:00</t>
+    <t>2023-11-15T19:14:31+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -543,7 +543,7 @@
   </si>
   <si>
     <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-inv-34:869: fixed value "completed" {null}inv-35:819: fixed value "in-progress" {null}inv-36:1555: fixed value "in-progress" {null}</t>
+inv-40:869: fixed value = completed if PRESCRIPTION - REFILL &gt; REFILL - RELEASED DATE/TIME (#52-52 &gt; 52.1-17) case not null {null}inv-41:819: fixed value = in-progress if PRESCRIPTION - REFILL &gt; REFILL - RELEASED DATE/TIME (#52-52 &gt; 52.1-17) case null {null}inv-42:1555: fixed value = in-progress if PRESCRIPTION - RELEASED DATE/TIME (#52-31) case null {null}</t>
   </si>
   <si>
     <t>Event.status</t>

--- a/docs/StructureDefinition-MedDispenseRefillMedicationDispense.xlsx
+++ b/docs/StructureDefinition-MedDispenseRefillMedicationDispense.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-11-15T19:14:31+00:00</t>
+    <t>2023-11-15T20:37:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -543,7 +543,7 @@
   </si>
   <si>
     <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-inv-40:869: fixed value = completed if PRESCRIPTION - REFILL &gt; REFILL - RELEASED DATE/TIME (#52-52 &gt; 52.1-17) case not null {null}inv-41:819: fixed value = in-progress if PRESCRIPTION - REFILL &gt; REFILL - RELEASED DATE/TIME (#52-52 &gt; 52.1-17) case null {null}inv-42:1555: fixed value = in-progress if PRESCRIPTION - RELEASED DATE/TIME (#52-31) case null {null}</t>
+inv-38:869: fixed value = completed if PRESCRIPTION - REFILL &gt; REFILL - RELEASED DATE/TIME (#52-52 &gt; 52.1-17) case not null {null}inv-39:819: fixed value = in-progress if PRESCRIPTION - REFILL &gt; REFILL - RELEASED DATE/TIME (#52-52 &gt; 52.1-17) case null {null}inv-40:1555: fixed value = in-progress if PRESCRIPTION - RELEASED DATE/TIME (#52-31) case null {null}</t>
   </si>
   <si>
     <t>Event.status</t>

--- a/docs/StructureDefinition-MedDispenseRefillMedicationDispense.xlsx
+++ b/docs/StructureDefinition-MedDispenseRefillMedicationDispense.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-11-15T20:37:43+00:00</t>
+    <t>2023-11-29T20:32:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-MedDispenseRefillMedicationDispense.xlsx
+++ b/docs/StructureDefinition-MedDispenseRefillMedicationDispense.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.5.0</t>
+    <t>0.6.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-11-29T20:32:59+00:00</t>
+    <t>2023-11-29T21:08:10+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -543,7 +543,7 @@
   </si>
   <si>
     <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-inv-38:869: fixed value = completed if PRESCRIPTION - REFILL &gt; REFILL - RELEASED DATE/TIME (#52-52 &gt; 52.1-17) case not null {null}inv-39:819: fixed value = in-progress if PRESCRIPTION - REFILL &gt; REFILL - RELEASED DATE/TIME (#52-52 &gt; 52.1-17) case null {null}inv-40:1555: fixed value = in-progress if PRESCRIPTION - RELEASED DATE/TIME (#52-31) case null {null}</t>
+inv-40:869: fixed value = completed if PRESCRIPTION - REFILL &gt; REFILL - RELEASED DATE/TIME (#52-52 &gt; 52.1-17) case not null {null}inv-41:819: fixed value = in-progress if PRESCRIPTION - REFILL &gt; REFILL - RELEASED DATE/TIME (#52-52 &gt; 52.1-17) case null {null}inv-42:1555: fixed value = in-progress if PRESCRIPTION - RELEASED DATE/TIME (#52-31) case null {null}</t>
   </si>
   <si>
     <t>Event.status</t>

--- a/docs/StructureDefinition-MedDispenseRefillMedicationDispense.xlsx
+++ b/docs/StructureDefinition-MedDispenseRefillMedicationDispense.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.6.0</t>
+    <t>0.7.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-11-29T21:08:10+00:00</t>
+    <t>2023-12-12T19:04:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
